--- a/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-冲突.xlsx
+++ b/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-冲突.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="R16164aa9bd2f46ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="R86b8434d164e4d75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,7 +338,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re79ffac801ba4814"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb6d2ce7b940413a"/>
   </x:tableParts>
 </x:worksheet>
 </file>